--- a/word-monitor-sub-domain/report/latest.xlsx
+++ b/word-monitor-sub-domain/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-11T00:59:52</t>
+          <t>2026-07-11T16:17:03</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -521,7 +521,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 42, "requestCount": 42, "successCount": 42, "successWithScoreCount": 42, "missingScoreCount": 0, "failedCount": 0}</t>
+          <t>{"inputCount": 28, "requestCount": 28, "successCount": 28, "successWithScoreCount": 28, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="31" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -618,17 +618,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>cinemana</t>
+          <t>game of thrones family tree</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>cinemana-two.vercel.app https://cinemana-two.vercel.app/</t>
+          <t>game-of-thrones-tree.vercel.app https://game-of-thrones-tree.vercel.app/</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>cinemana</t>
+          <t>game of thrones family tree</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -638,61 +638,59 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>1058.696</t>
+          <t>808.536364</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>89720.0</t>
+          <t>28690.0</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>19770.0</t>
+          <t>34950.0</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>33.3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>digibouquet</t>
+          <t>enamed ranking</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>digibouquet.vercel.app https://digibouquet.vercel.app/
-digibouquet.vercel.app https://digibouquet.vercel.app/garden
-digitalbouquet.vercel.app https://digitalbouquet.vercel.app/</t>
+          <t>dados-enamed.vercel.app https://dados-enamed.vercel.app/</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>digibouquet</t>
+          <t>enamed ranking</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -702,27 +700,27 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>555.294915</t>
+          <t>8.492857</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>44880.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>2030.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="J3" s="5" t="n"/>
@@ -733,24 +731,24 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>42.3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>memento mori calendar</t>
+          <t>チームみらい</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>memento-mori-calendar.vercel.app https://memento-mori-calendar.vercel.app/</t>
+          <t>sns-profile-site.vercel.app https://sns-profile-site.vercel.app/</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>memento mori calendar</t>
+          <t>チームみらい</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -758,64 +756,57 @@
           <t>both（SIM+SEM）</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>429.0</t>
-        </is>
-      </c>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2860.0</t>
+          <t>61400.0</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1950.0</t>
+          <t>52270.0</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>imagine explainers</t>
+          <t>camera with filters</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>explainers-site.vercel.app https://explainers-site.vercel.app/
-explainers-site.vercel.app https://explainers-site.vercel.app/explainers
-explainers-site.vercel.app https://explainers-site.vercel.app/videos/6972ee05d5c7f0406e331a47
-explainers-site.vercel.app https://explainers-site.vercel.app/videos</t>
+          <t>ar-webcam.vercel.app https://ar-webcam.vercel.app/</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>imagine explainers</t>
+          <t>camera with filters</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -823,61 +814,57 @@
           <t>both（SIM+SEM）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>391.44</t>
-        </is>
-      </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>27960.0</t>
+          <t>1280.0</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>16110.0</t>
+          <t>23460.0</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>38.8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>シス単</t>
+          <t>dutamovie21</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>system-english-quiz.vercel.app https://system-english-quiz.vercel.app/</t>
+          <t>dutamovie21org.vercel.app https://dutamovie21org.vercel.app/</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>シス単</t>
+          <t>dutamovie21</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -885,32 +872,32 @@
           <t>both（SIM+SEM）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>289.333333</t>
-        </is>
-      </c>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>8680.0</t>
+          <t>209930.0</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>27190.0</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n"/>
+          <t>21580.0</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -918,24 +905,24 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>48.6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>random key generator</t>
+          <t>نتيجه ثانويه عامه 2024</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>secretkeygen.vercel.app https://secretkeygen.vercel.app/</t>
+          <t>thanawaya-results.vercel.app https://thanawaya-results.vercel.app/</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>random key generator</t>
+          <t>نتيجه ثانويه عامه 2024</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -943,36 +930,28 @@
           <t>both（SIM+SEM）</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>31.685294</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>3990.0</t>
+          <t>2100.0</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>3480.0</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
+          <t>8150.0</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -980,24 +959,24 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>44.2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>seabank login</t>
+          <t>mangapiracy</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>laravel-seabank.vercel.app https://laravel-seabank.vercel.app/</t>
+          <t>piracy.vercel.app https://piracy.vercel.app/type/comics-and-manga</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>seabank login</t>
+          <t>mangapiracy</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1005,32 +984,32 @@
           <t>both（SIM+SEM）</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>10.412987</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>4220.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="n"/>
+          <t>570.0</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>27.0</t>
+        </is>
+      </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1038,24 +1017,24 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>福岡 貯水率</t>
+          <t>fennec presets</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>click-me-site.vercel.app https://click-me-site.vercel.app/dam-fukuoka-mizu</t>
+          <t>rocket-presets.vercel.app https://rocket-presets.vercel.app/index.html</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>福岡 貯水率</t>
+          <t>fennec presets</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1066,12 +1045,12 @@
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>24800.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -1081,31 +1060,39 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>5400.0</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>32.3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>intel graphics control panel</t>
+          <t>kira website death note</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>bluecpu.vercel.app https://bluecpu.vercel.app/articles/k/ka/kak-ustanovit-intel-graphics-control-panel-na-windows-10.html</t>
+          <t>kira-website.vercel.app https://kira-website.vercel.app/</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>intel graphics control panel</t>
+          <t>kira website death note</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1116,12 +1103,12 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>5900.0</t>
+          <t>1710.0</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
@@ -1131,14 +1118,10 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>4430.0</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
+          <t>230.0</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1146,24 +1129,24 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>60.7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>rhyme game</t>
+          <t>mirexa vercel app</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>rhyme-game2026.vercel.app https://rhyme-game2026.vercel.app/</t>
+          <t>mirexa.vercel.app https://mirexa.vercel.app/</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>rhyme game</t>
+          <t>mirexa vercel app</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1174,12 +1157,12 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>21140.0</t>
+          <t>580.0</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1189,39 +1172,31 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>3330.0</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>34.0</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>65.8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>проверка реакции</t>
+          <t>cursor token usage</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>reactiontimetest.vercel.app https://reactiontimetest.vercel.app/</t>
+          <t>cursortokens.vercel.app https://cursortokens.vercel.app/</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>проверка реакции</t>
+          <t>cursor token usage</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1232,12 +1207,12 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>5030.0</t>
+          <t>1900.0</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
@@ -1247,35 +1222,35 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>2810.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>72.3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>vit placement tracker</t>
+          <t>какие лодки пвх не подлежат регистрации</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>placement-tracker-vit-2026.vercel.app https://placement-tracker-vit-2026.vercel.app/</t>
+          <t>lodkamaster.vercel.app https://lodkamaster.vercel.app/articles/k/ka/kakie-lodki-nado-registrirovat.html</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>vit placement tracker</t>
+          <t>какие лодки пвх не подлежат регистрации</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1261,7 @@
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>5410.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -1301,35 +1276,31 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>2420.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="K13" s="5" t="n"/>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>animovie</t>
+          <t>witch hat atelier spell maker</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>animovie-green.vercel.app https://animovie-green.vercel.app/</t>
+          <t>wha-spell-simulator.vercel.app https://wha-spell-simulator.vercel.app/</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>animovie</t>
+          <t>witch hat atelier spell maker</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1340,7 +1311,7 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>2950.0</t>
+          <t>20110.0</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1355,39 +1326,31 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>970.0</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>27.7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>shadcn map</t>
+          <t>dazn mundial acestream</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>shadcn-map.vercel.app https://shadcn-map.vercel.app/</t>
+          <t>markel-links.vercel.app https://markel-links.vercel.app/</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>shadcn map</t>
+          <t>dazn mundial acestream</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1398,12 +1361,12 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>2130.0</t>
+          <t>6200.0</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1413,39 +1376,31 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>39.4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>mermaid to excalidraw</t>
+          <t>joseph chio portfolio</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>mermaid-to-excalidraw.vercel.app https://mermaid-to-excalidraw.vercel.app/</t>
+          <t>josephchio.vercel.app https://josephchio.vercel.app/</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>mermaid to excalidraw</t>
+          <t>joseph chio portfolio</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1456,12 +1411,12 @@
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>1590.0</t>
+          <t>1480.0</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1471,39 +1426,31 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>270.0</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>22.0</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>31.6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>once human character preset</t>
+          <t>line ranger kiwi</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>once-human-library.vercel.app https://once-human-library.vercel.app/</t>
+          <t>line-ranger-kiwi.vercel.app https://line-ranger-kiwi.vercel.app/</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>once human character preset</t>
+          <t>line ranger kiwi</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1514,7 +1461,7 @@
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>820.0</t>
+          <t>1310.0</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1529,35 +1476,31 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>51.2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>download google drive restricted pdf</t>
+          <t>ジェネシスパス</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>fancy-notes.vercel.app https://fancy-notes.vercel.app/230304_2057</t>
+          <t>maplestory-jp.vercel.app https://maplestory-jp.vercel.app/genesis</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>download google drive restricted pdf</t>
+          <t>ジェネシスパス</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1568,12 +1511,12 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>540.0</t>
+          <t>1290.0</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
@@ -1583,35 +1526,31 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>60.2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>คํานวนไทยช่วยไทยพลัส</t>
+          <t>gta5 radio site</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>promchaitang.vercel.app https://promchaitang.vercel.app/</t>
+          <t>gtav-radio-nine.vercel.app https://gtav-radio-nine.vercel.app/</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>คํานวนไทยช่วยไทยพลัส</t>
+          <t>gta5 radio site</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1622,7 +1561,7 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>21450.0</t>
+          <t>1080.0</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1644,24 +1583,24 @@
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>39.1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>pagame rata</t>
+          <t>aeron james castillo</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>pagamerata.vercel.app https://pagamerata.vercel.app/</t>
+          <t>ajcastillo.vercel.app https://ajcastillo.vercel.app/</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>pagame rata</t>
+          <t>aeron james castillo</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1672,7 +1611,7 @@
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>2800.0</t>
+          <t>1040.0</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1694,24 +1633,24 @@
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>48.7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>تصحيح عربية باك 2026</t>
+          <t>cricfusion</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>bacstory.vercel.app https://bacstory.vercel.app/bac-2026-sci-arabe-corrige</t>
+          <t>cricfusion.vercel.app https://cricfusion.vercel.app/</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>تصحيح عربية باك 2026</t>
+          <t>cricfusion</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1722,7 +1661,7 @@
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>2400.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1744,24 +1683,24 @@
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>49.9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>swe marathon</t>
+          <t>air draw gesture</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>swe-marathon.vercel.app https://swe-marathon.vercel.app/</t>
+          <t>air-draw-one.vercel.app https://air-draw-one.vercel.app/</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>swe marathon</t>
+          <t>air draw gesture</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1772,7 +1711,7 @@
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>2080.0</t>
+          <t>550.0</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1794,24 +1733,24 @@
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>47.3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>fifaphy</t>
+          <t>인상율</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>fifaphy.vercel.app https://fifaphy.vercel.app/</t>
+          <t>salary-calc-fe.vercel.app https://salary-calc-fe.vercel.app/salary3</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>fifaphy</t>
+          <t>인상율</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1822,7 +1761,7 @@
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>1990.0</t>
+          <t>440.0</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1844,24 +1783,25 @@
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>29.8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sakuraze</t>
+          <t>docx в markdown</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>sakuraze.vercel.app https://sakuraze.vercel.app/</t>
+          <t>word2markdown.vercel.app https://word2markdown.vercel.app/ru
+markdownvisualizer.vercel.app https://markdownvisualizer.vercel.app/word-to-markdown</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>sakuraze</t>
+          <t>docx в markdown</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1872,12 +1812,12 @@
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>1450.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -1894,25 +1834,24 @@
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>36.9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>캄몬</t>
+          <t>download gta vice city free online</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>mstzsite.vercel.app https://mstzsite.vercel.app/
-monstarznew.vercel.app https://monstarznew.vercel.app/</t>
+          <t>gtabrowser.vercel.app https://gtabrowser.vercel.app/</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>캄몬</t>
+          <t>download gta vice city free online</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1923,7 +1862,7 @@
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>1240.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -1945,47 +1884,35 @@
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>54.6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>curso caio alessi preço</t>
+          <t>fuck claude vercel.app</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>caioalessi.vercel.app https://caioalessi.vercel.app/contato</t>
+          <t>fuck-claude.vercel.app https://fuck-claude.vercel.app/</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>curso caio alessi preço</t>
+          <t>fuck claude vercel.app</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>910.0</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1995,24 +1922,24 @@
       <c r="K26" s="5" t="n"/>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>86.5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>cutting mat bg</t>
+          <t>как установить стеклоподъемник на ваз 21214</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>cutting-mat-generator.vercel.app https://cutting-mat-generator.vercel.app/</t>
+          <t>master-elektriki.vercel.app https://master-elektriki.vercel.app/articles/u/us/ustanovka-steklopodemnikov-na-nivu-21214.html?ysclid=mr5on9kw6r118625617</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>cutting mat bg</t>
+          <t>как установить стеклоподъемник на ваз 21214</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2023,7 +1950,7 @@
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>830.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2045,24 +1972,24 @@
       <c r="K27" s="5" t="n"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>19.6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>better input sharkpool</t>
+          <t>лучшие масла для смазки электробритвы</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>sharkpools-extensions.vercel.app https://sharkpools-extensions.vercel.app/</t>
+          <t>maslo-wiki.vercel.app https://maslo-wiki.vercel.app/articles/m/ma/maslo-dlya-britvennoj-mashinki.html</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>better input sharkpool</t>
+          <t>лучшие масла для смазки электробритвы</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2073,12 +2000,12 @@
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
@@ -2095,24 +2022,24 @@
       <c r="K28" s="5" t="n"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>7.1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>fwc2026 knockout vercel</t>
+          <t>почему плохо грузит вк на 11 айфоне</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>fwc2026-knockout.vercel.app https://fwc2026-knockout.vercel.app/</t>
+          <t>iphone-info.vercel.app https://iphone-info.vercel.app/messendzhery-i-sotsseti/p/po/pochemu-tupit-vk-na-ajfone-11.html</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>fwc2026 knockout vercel</t>
+          <t>почему плохо грузит вк на 11 айфоне</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2123,7 +2050,7 @@
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>630.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2145,665 +2072,12 @@
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>57.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>selection way e leak spidey</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>spidyway.vercel.app https://spidyway.vercel.app/</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>selection way e leak spidey</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>590.0</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>im a young god novel</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>sakuraze.vercel.app https://sakuraze.vercel.app/novel/im-a-young-god-wont-you-raise-me</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>im a young god novel</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>470.0</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>1с добавить команду создать на основании</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>1c-expert.vercel.app https://1c-expert.vercel.app/articles/k/ka/kak-dobavit-knopku-vvoda-na-osnovanii-v-dokument-1s.html
-1c-expert.vercel.app https://1c-expert.vercel.app/articles/k/ka/kak-dobavit-komandu-sozdat-na-osnovanii-1s.html</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>1с добавить команду создать на основании</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>calculate total length of content on a channel youtube</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>ytp-length.vercel.app https://ytp-length.vercel.app/tools/youtube-channel-length</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>calculate total length of content on a channel youtube</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>tod calc</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>descent.vercel.app https://descent.vercel.app/</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>tod calc</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>tính điểm học bạ tmu</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>admission-calculator-taupe.vercel.app https://admission-calculator-taupe.vercel.app/</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>tính điểm học bạ tmu</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>uth tính điểm</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>uth-calculator-2026.vercel.app https://uth-calculator-2026.vercel.app/</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>uth tính điểm</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>где посмотреть привязку карты на озоне на сайте</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>obozone.vercel.app https://obozone.vercel.app/articles/o/oz/ozon-sokhranennye-karty-gde.html</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>где посмотреть привязку карты на озоне на сайте</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>как вытащить ящик с шариковыми направляющими</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>asia-motors-hub.vercel.app https://asia-motors-hub.vercel.app/articles/k/ka/kak-vynut-yashchik-iz-napravlyayushchikh-komoda.html</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>как вытащить ящик с шариковыми направляющими</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="5" t="n"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>как извлечь жесткий диск из нетбука днс модель dns 0121597</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>nissan-expert.vercel.app https://nissan-expert.vercel.app/articles/k/ka/kak-razobrat-noutbuk-dns.html</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>как извлечь жесткий диск из нетбука днс модель dns 0121597</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="5" t="n"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>как открыть мультибрендовый пвз в одном месте</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>obozone.vercel.app https://obozone.vercel.app/articles/k/ka/kak-otkryt-valberis-i-ozon-v-odnom-meste.html</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>как открыть мультибрендовый пвз в одном месте</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ремонт робота пылесоса медея м7 своими руками</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>sos-pylesos.vercel.app https://sos-pylesos.vercel.app/articles/m/mi/midea-robot-pylesos-kak-perezagruzit.html</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>ремонт робота пылесоса медея м7 своими руками</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>стоисть 260 еудупкфь ыефкы</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>calc-tg-stars.vercel.app https://calc-tg-stars.vercel.app/</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>стоисть 260 еудупкфь ыефкы</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>熱中症 緊急連絡先 テンプレート</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>heatstroke-navi.vercel.app https://heatstroke-navi.vercel.app/articles/heatstroke-reporting-system-template</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>熱中症 緊急連絡先 テンプレート</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>4.3</t>
+          <t>22.7</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sub-domain/report/latest.xlsx
+++ b/word-monitor-sub-domain/report/latest.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-12T20:08:19</t>
+          <t>2026-07-13T19:33:58</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260712-200758</t>
+          <t>20260713-193335</t>
         </is>
       </c>
     </row>
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260712-130634</t>
+          <t>20260713-174447</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +577,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/report-20260712-200758.md</t>
+          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/report-20260713-193335.md</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/keyword-table-20260712-200758.xlsx</t>
+          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/keyword-table-20260713-193335.xlsx</t>
         </is>
       </c>
     </row>

--- a/word-monitor-sub-domain/report/latest.xlsx
+++ b/word-monitor-sub-domain/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -32,12 +34,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +64,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -422,174 +455,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>generatedAt</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>vercel.app</t>
+          <t>2026-07-14T11:49:31</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generatedAt</t>
+          <t>standardWordTableVersion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-13T19:33:58</t>
+          <t>v1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stamp</t>
+          <t>scoreFormula</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260713-193335</t>
+          <t>simWindowVolume * simCpc / simKd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>baselineMode</t>
-        </is>
-      </c>
-      <c r="B4" t="b">
-        <v>0</v>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>check-gefei-kd</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>baselineStamp</t>
+          <t>inputMode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260713-174447</t>
+          <t>standard_word_table</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pagesFetched</t>
+          <t>rowCount</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dedupedRows</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>subdomainCount</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>reportRows</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>standardWordRows</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>newPageKeywordRows</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>newSubdomainKeywordRows</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>standardWordTableVersion</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>reportHistoryPath</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/report-20260713-193335.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>excelHistoryPath</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/keyword-table-20260713-193335.xlsx</t>
+          <t>gefeiKdSummary</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"inputCount": 21, "requestCount": 21, "successCount": 21, "successWithScoreCount": 21, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -604,20 +555,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="59" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -683,8 +634,867 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>lion parcel</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://lionparcel.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>393.90411</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>191700</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>373780</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>lion parcel</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>kcd interactive map</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://kingdomcomemap.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="4" t="n">
+        <v>2110</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>kcd interactive map</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>hero siege items</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://hero-siege-helper.vercel.app/items</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="4" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>450</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>hero siege items</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>угадай цвет персонажа</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://toontone.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="4" t="n">
+        <v>10490</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>угадай цвет персонажа</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>suite tv</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://suite-tv.vercel.app/en</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="4" t="n">
+        <v>15130</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>suite tv</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>12 word phrase generator</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://seed-phrases-demo.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12 word phrase generator</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>butterstream</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://butterstream.vercel.app/
+https://butterstream.vercel.app/watch/football</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="4" t="n">
+        <v>14470</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>butterstream</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>letterboxd top 4 match</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://lettermatchd-web.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="4" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>letterboxd top 4 match</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>what dbd killer should i play</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://who-is-your-ideal-killer.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="4" t="n">
+        <v>710</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>what dbd killer should i play</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>leetify-dun</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://leetify-dun.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="4" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="8" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>leetify-dun</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>yakithesapla.net</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://yakithesapla.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="4" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>yakithesapla.net</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>fe engage calc</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://fengage-calc.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="4" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>fe engage calc</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>dsa algorithm visualization</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://dsa-visualizer-delta.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="4" t="n">
+        <v>610</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>dsa algorithm visualization</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>fc26 sbc free chrome extension</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://autopilotsbc.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="4" t="n">
+        <v>520</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>fc26 sbc free chrome extension</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>glow nails babelsberg</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://glownails-babelsberg.vercel.app/de</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>glow nails babelsberg</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>нейрохам онлайн</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://neiroham2-0.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>нейрохам онлайн</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>russia virtual sms sim only</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://onlinesim-ru.vercel.app/free_numbers/russia</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>russia virtual sms sim only</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>sberbank.com/sms/pay</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://pairaipot.vercel.app/sberbank-com-sms-pay-chto-eto.html</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="8" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>sberbank.com/sms/pay</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>какое напряжение в кулере ноутбука асер</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://nissan-expert.vercel.app/articles/r/ra/raspinovka-kulera-noutbuka-4-pin.html</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>какое напряжение в кулере ноутбука асер</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>кредитка от альфа банка как работает беспроцентный период</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://alfa-gid.vercel.app/articles/k/ka/kak-prodlit-besprotsentnyj-period-alfa-bank.html</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="8" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>кредитка от альфа банка как работает беспроцентный период</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>스마트스테이션 드라이버</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://st-edge-search.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="8" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>스마트스테이션 드라이버</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sub-domain/report/latest.xlsx
+++ b/word-monitor-sub-domain/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -32,12 +34,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +64,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -422,174 +455,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>generatedAt</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>vercel.app</t>
+          <t>2026-07-16T23:07:49</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generatedAt</t>
+          <t>standardWordTableVersion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-15T13:51:31</t>
+          <t>v1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stamp</t>
+          <t>scoreFormula</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20260715-135109</t>
+          <t>simWindowVolume * simCpc / simKd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>baselineMode</t>
-        </is>
-      </c>
-      <c r="B4" t="b">
-        <v>0</v>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>check-gefei-kd</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>baselineStamp</t>
+          <t>inputMode</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20260714-113942</t>
+          <t>standard_word_table</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pagesFetched</t>
+          <t>rowCount</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dedupedRows</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>subdomainCount</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>reportRows</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>standardWordRows</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>newPageKeywordRows</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>newSubdomainKeywordRows</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>standardWordTableVersion</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>reportHistoryPath</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/report-20260715-135109.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>excelHistoryPath</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>/Users/bytedance/work/raxskle/sitte/ai/word-monitor-sub-domain/report/history/keyword-table-20260715-135109.xlsx</t>
+          <t>gefeiKdSummary</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{"inputCount": 44, "requestCount": 44, "successCount": 44, "successWithScoreCount": 44, "missingScoreCount": 0, "failedCount": 0}</t>
         </is>
       </c>
     </row>
@@ -604,20 +555,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="68" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -683,8 +634,1843 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>яндекс погода</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://yandex-weather.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>83847.60000000001</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>2794920</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1664350</v>
+      </c>
+      <c r="H2" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>яндекс погода</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>flixer</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://theflixer.vercel.app/
+https://flixr-beta.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>15024.115942</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1026400</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>885940</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>flixer</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>scheme</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://scheme-seva-gov.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1868.467925</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>215280</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>151240</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>scheme</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>micromodal</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://micromodal.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>751.8</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>7160</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>8690</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>micromodal</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>mirexa</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://mirexa.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>446.35</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>1130</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1370</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>mirexa</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>the path into the abyss</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://thepathintotheabyssweb.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>171.272727</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>15700</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1640</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>the path into the abyss</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>конвертировать jpg в webp</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://webp-to.vercel.app/convert/jpg-to-webp</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>6.825</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1170</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>320</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>конвертировать jpg в webp</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>latasa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://latasa.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="4" t="n">
+        <v>5060</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>10260</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>latasa</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>stick it with robert</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://stick-it-with-robert.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="4" t="n">
+        <v>1930</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>4210</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>stick it with robert</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>crt filter</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://pixelcrt.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="4" t="n">
+        <v>14030</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>3370</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>crt filter</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>classement fifa live</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://fifa-rankings.vercel.app/fr</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="4" t="n">
+        <v>10450</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2610</v>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>classement fifa live</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>snail ide</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://snailshare.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1430</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>snail ide</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>作戦室</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://jervis.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>880</v>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>作戦室</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>laravel app key generator</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://laravel-encryption-key-generator.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>800</v>
+      </c>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>laravel app key generator</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>rvce placements</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://rvce-placements.vercel.app/placements/2025</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>rvce placements</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>eaglecraft 1.20</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://eaglercraft-1-20-4.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>540</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>eaglecraft 1.20</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>suite tv</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://suite-tv.vercel.app/en
+https://suite-tv.vercel.app/fr
+https://suite-tv.vercel.app/es</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="4" t="n">
+        <v>26470</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>410</v>
+      </c>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>suite tv</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>leiptr</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://old-icelandic.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>330</v>
+      </c>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>leiptr</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>sunnify</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://sunnify-spotify-downloader.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>190</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>sunnify</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>find my roomie</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://srmfindmyroomie.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="4" t="n">
+        <v>1210</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>find my roomie</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>skillui</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://skillui.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="4" t="n">
+        <v>2210</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="8" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>skillui</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>vit 360</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://vit360.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="4" t="n">
+        <v>1780</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>vit 360</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>php on vercel</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://php-app-vercel.vercel.app/tutorial</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="4" t="n">
+        <v>730</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>php on vercel</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>minecraft spawn sound effect</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://minecraft-sounds.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="8" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>minecraft spawn sound effect</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>13ftladder</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://13ft-ladder.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="4" t="n">
+        <v>860</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>13ftladder</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>jiit shelf</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://jiitshelf.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="4" t="n">
+        <v>1590</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>jiit shelf</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>driver livery monoposto</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://monopostostore.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="8" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>driver livery monoposto</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>coderush.games</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://coderushx.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="4" t="n">
+        <v>74370</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="8" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>coderush.games</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>nhpr.abdm.gov.in login</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://nhpr-registration.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="4" t="n">
+        <v>14290</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
+      <c r="J30" s="8" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>nhpr.abdm.gov.in login</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>아디나의 분석실</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://adina-crystal-ball.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="4" t="n">
+        <v>9520</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="8" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>아디나의 분석실</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>cps-test-tool.vercel</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://cps-test-tool.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="4" t="n">
+        <v>3680</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="8" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>cps-test-tool.vercel</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>grid noise animator</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://grid-noise-animator.vercel.app/en.html</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="4" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="8" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>grid noise animator</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>vit ap faculty ranker</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://vitor-facultyranker.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="4" t="n">
+        <v>2750</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>vit ap faculty ranker</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>autocad linetype generator</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://autocad-linetype-builder.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="4" t="n">
+        <v>860</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>autocad linetype generator</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>zepto app me referral code kaise nikale</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://zepto-refferal-code.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n"/>
+      <c r="D36" s="4" t="n">
+        <v>720</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>zepto app me referral code kaise nikale</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>sito tavolara calcio</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://tavolara-calcio.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="4" t="n">
+        <v>670</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="8" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>sito tavolara calcio</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>recurrence tree visualizer</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://recursion.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n"/>
+      <c r="D38" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n"/>
+      <c r="I38" s="7" t="n"/>
+      <c r="J38" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>recurrence tree visualizer</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>syccmcc syc350 настройка карбюратора</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://motokvadro.vercel.app/articles/k/ka/kak-nastroit-karbyurator-na-mototsikle-enduro.html</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="7" t="n"/>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>syccmcc syc350 настройка карбюратора</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>vercel pro github student discount</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://studentbenefits.vercel.app/tools/githubedu</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="8" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>vercel pro github student discount</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>где все болты на панели ваз 2110</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>https://vaz-master.vercel.app/articles/k/kr/krepleniya-torpedy-vaz-2110.html?ysclid=mr263cm4o984326568</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n"/>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="8" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>где все болты на панели ваз 2110</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>оприходование основного средства в 1с 8.3 пошаговая инструкция</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://1c-expert.vercel.app/articles/k/ka/kak-postavit-na-uchet-os-v-1s-8.html</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>оприходование основного средства в 1с 8.3 пошаговая инструкция</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>оприходование основного средства в 1с нулевой остаточной стоимости</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>https://1c-expert.vercel.app/articles/o/os/osnovnoe-sredstvo-samortizirovano-chto-delat-dalshe-v-1s.html</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>оприходование основного средства в 1с нулевой остаточной стоимости</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>полутон фильм 2025</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://codedex.vercel.app/python/10-currency</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="8" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>полутон фильм 2025</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>признаки износа подушек двигателя ваз гранта 8 кл</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>https://lada-spravka.vercel.app/articles/l/la/lada-granta-kreplenie-dvigatelya.html</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n"/>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>признаки износа подушек двигателя ваз гранта 8 кл</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/word-monitor-sub-domain/report/latest.xlsx
+++ b/word-monitor-sub-domain/report/latest.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-07-30T13:54:56</t>
+          <t>2026-08-01T14:28:54</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"inputCount": 75, "requestCount": 75, "successCount": 75, "successWithScoreCount": 75, "missingScoreCount": 0, "failedCount": 0}</t>
+          <t>{"inputCount": 88, "requestCount": 88, "successCount": 37, "successWithScoreCount": 37, "missingScoreCount": 0, "failedCount": 51}</t>
         </is>
       </c>
     </row>
@@ -555,10 +555,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="66" customWidth="1" min="1" max="1"/>
+    <col width="61" customWidth="1" min="1" max="1"/>
     <col width="64" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -568,7 +568,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="66" customWidth="1" min="11" max="11"/>
+    <col width="61" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -637,41 +637,39 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>biglobe メール</t>
+          <t>cinemark</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>https://biglobemailsjp.vercel.app/</t>
+          <t>https://cinemark-peru.vercel.app/</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>16618.105263</v>
+        <v>23411</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>394680</v>
+        <v>7023300</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>135710</v>
+        <v>5984550</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>90.7</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="J2" s="8" t="n"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>biglobe メール</t>
+          <t>cinemark</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -683,41 +681,39 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>الزمالك</t>
+          <t>streamx</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://zamalek.vercel.app/</t>
+          <t>https://streamx-xi.vercel.app/?category=tv</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>13677.314286</v>
+        <v>14072.280702</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>323450</v>
+        <v>802120</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>1.48</v>
+        <v>1</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>3136630</v>
+        <v>94060</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>48.7</v>
-      </c>
+        <v>0.57</v>
+      </c>
+      <c r="J3" s="8" t="n"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>الزمالك</t>
+          <t>streamx</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -729,41 +725,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>misumi</t>
+          <t>the paradise</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://order-web-jp.vercel.app/</t>
+          <t>https://theparadisemovie.vercel.app/</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8789.835294</v>
+        <v>10690.618182</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>233480</v>
+        <v>367490</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.28</v>
+        <v>0.64</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>344890</v>
+        <v>78820</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>48.5</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="J4" s="8" t="n"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>misumi</t>
+          <t>the paradise</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -775,41 +769,41 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>sandboxels</t>
+          <t>misumi</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://shalbito.vercel.app/</t>
+          <t>https://order-web-jp.vercel.app/</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4311.619048</v>
+        <v>8627.200000000001</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>226360</v>
+        <v>229160</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4</v>
+        <v>1.28</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>216820</v>
+        <v>344890</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>62.8</v>
+        <v>48.5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>sandboxels</t>
+          <t>misumi</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -821,41 +815,41 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>moviedex</t>
+          <t>نتيجة الثانوية العامة</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://moviedex-client.vercel.app/</t>
+          <t>https://nategaeg.vercel.app/</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4249.381818</v>
+        <v>6077.952</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>333880</v>
+        <v>237420</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>21130</v>
+        <v>66170</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>34</v>
+        <v>67.5</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>moviedex</t>
+          <t>نتيجة الثانوية العامة</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -867,42 +861,41 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>tmdb</t>
+          <t>moviedex</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://tmdb-pearl.vercel.app/
-https://tmdb-clone-sk.vercel.app/</t>
+          <t>https://moviedex-client.vercel.app/</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3881.78</v>
+        <v>4184.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>633760</v>
+        <v>328790</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>182910</v>
+        <v>21130</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>68.40000000000001</v>
+        <v>34</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>tmdb</t>
+          <t>moviedex</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -914,41 +907,39 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>cinemaos</t>
+          <t>ragnarok origin classic</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://cinemaos-v2.vercel.app/</t>
+          <t>https://ragnarok-origin-classic-fan-blog.vercel.app/</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3686</v>
+        <v>1648.881818</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>73720</v>
+        <v>259110</v>
       </c>
       <c r="E8" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>22180</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>9240</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>27</v>
-      </c>
       <c r="I8" s="7" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>52.8</v>
-      </c>
+        <v>5.7</v>
+      </c>
+      <c r="J8" s="8" t="n"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>cinemaos</t>
+          <t>ragnarok origin classic</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -960,41 +951,39 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>نتيجه الثانويه العامه</t>
+          <t>movie mod</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://nategaeg.vercel.app/</t>
+          <t>https://moviesmod.vercel.app/</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1584.483333</v>
+        <v>1273.015873</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>73130</v>
+        <v>200500</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>77720</v>
+        <v>51050</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>45.5</v>
-      </c>
+        <v>1.34</v>
+      </c>
+      <c r="J9" s="8" t="n"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>نتيجه الثانويه العامه</t>
+          <t>movie mod</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1006,41 +995,39 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ragnarok origin classic</t>
+          <t>screened</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://ragnarok-origin-classic-fan-blog.vercel.app/</t>
+          <t>https://getscreened.vercel.app/</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1459.754545</v>
+        <v>586.676471</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>229390</v>
+        <v>3050</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.35</v>
+        <v>3.27</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>22180</v>
+        <v>74200</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <v>40.5</v>
-      </c>
+        <v>3.46</v>
+      </c>
+      <c r="J10" s="8" t="n"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>ragnarok origin classic</t>
+          <t>screened</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1052,41 +1039,39 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>movie mod</t>
+          <t>auto sbc</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://moviesmod.vercel.app/</t>
+          <t>https://autopilotsbc.vercel.app/</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1273.333333</v>
+        <v>490.583333</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>200550</v>
+        <v>20300</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>51050</v>
+        <v>9890</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>42.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="n"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>movie mod</t>
+          <t>auto sbc</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1098,41 +1083,39 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>connections answers today</t>
+          <t>speeky</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://connectionsanswer.vercel.app/</t>
+          <t>https://speeky-beta.vercel.app/</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>838.759184</v>
+        <v>123.386301</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>120880</v>
+        <v>4170</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.34</v>
+        <v>2.16</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>165380</v>
+        <v>1850</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>57.3</v>
-      </c>
+        <v>2.39</v>
+      </c>
+      <c r="J12" s="8" t="n"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>connections answers today</t>
+          <t>speeky</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1144,39 +1127,39 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>シス単</t>
+          <t>karar çarkı</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://system-english-quiz.vercel.app/</t>
+          <t>https://karar-carki.vercel.app/</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>514.333333</v>
+        <v>83.657143</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>15430</v>
+        <v>21960</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>27190</v>
-      </c>
-      <c r="H13" s="7" t="n"/>
+        <v>28170</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>22</v>
+      </c>
       <c r="I13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>43.9</v>
-      </c>
+      <c r="J13" s="8" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>シス単</t>
+          <t>karar çarkı</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1188,37 +1171,39 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>gemini prompt vercel app</t>
+          <t>럭키글라이드</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://gemini-prompts.vercel.app/</t>
+          <t>https://luckyglide.vercel.app/</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>198.64</v>
+        <v>48.829091</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3820</v>
+        <v>3730</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>18150</v>
+        <v>160</v>
       </c>
       <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
+      <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J14" s="8" t="n">
-        <v>52.9</v>
+        <v>59.4</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>gemini prompt vercel app</t>
+          <t>럭키글라이드</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1230,41 +1215,39 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>karar çarkı</t>
+          <t>seneago</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://karar-carki.vercel.app/</t>
+          <t>https://gosaneago2025.vercel.app/</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>76.304762</v>
+        <v>4.946809</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>20030</v>
+        <v>250</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.24</v>
+        <v>0.93</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>28170</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>22</v>
-      </c>
+        <v>2480</v>
+      </c>
+      <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>58.1</v>
+        <v>24.6</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>karar çarkı</t>
+          <t>seneago</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1276,39 +1259,38 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>럭키글라이드</t>
+          <t>spidey universe</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://luckyglide.vercel.app/</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>37.44</v>
-      </c>
+          <t>https://spidyuniverserwa.vercel.app/
+https://spidyway.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="4" t="n">
-        <v>2860</v>
+        <v>17760</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>160</v>
+        <v>35950</v>
       </c>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>59.4</v>
+        <v>37.4</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>럭키글라이드</t>
+          <t>spidey universe</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1320,39 +1302,39 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>topsters</t>
+          <t>criterion closet</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://usic-tools.vercel.app/topsters.html</t>
+          <t>https://the-criterion-closet.vercel.app/</t>
         </is>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="4" t="n">
-        <v>22660</v>
+        <v>48530</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>39050</v>
+        <v>11560</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>40.1</v>
+        <v>60.6</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>topsters</t>
+          <t>criterion closet</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1364,18 +1346,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>spidey universe</t>
+          <t>skyanime</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://spidyuniverserwa.vercel.app/
-https://spidyway.vercel.app/</t>
+          <t>https://iamlegend.vercel.app/</t>
         </is>
       </c>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="4" t="n">
-        <v>15760</v>
+        <v>2200</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
@@ -1384,18 +1365,18 @@
         <v>0</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>35950</v>
-      </c>
-      <c r="H18" s="7" t="n"/>
+        <v>10260</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>24</v>
+      </c>
       <c r="I18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>37.4</v>
-      </c>
+      <c r="J18" s="8" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>spidey universe</t>
+          <t>skyanime</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1407,39 +1388,37 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>criterion closet</t>
+          <t>enchantment calculator</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://the-criterion-closet.vercel.app/</t>
+          <t>https://minecraft-enchantment-order.vercel.app/</t>
         </is>
       </c>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="4" t="n">
-        <v>42550</v>
+        <v>13690</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>11560</v>
+        <v>6660</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="8" t="n">
-        <v>60.6</v>
-      </c>
+      <c r="J19" s="8" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>criterion closet</t>
+          <t>enchantment calculator</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1451,35 +1430,37 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>4 elementos ordem paranormal</t>
+          <t>vega app</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://4elementos.vercel.app/</t>
+          <t>https://vegaapp.vercel.app/</t>
         </is>
       </c>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="4" t="n">
-        <v>1560</v>
+        <v>12100</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4420</v>
-      </c>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="8" t="n">
-        <v>53.7</v>
-      </c>
+        <v>3370</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="8" t="n"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4 elementos ordem paranormal</t>
+          <t>vega app</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1491,39 +1472,37 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>aniway</t>
+          <t>奥维地图</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://aniway.vercel.app/</t>
+          <t>https://ov-map.vercel.app/</t>
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="4" t="n">
-        <v>7290</v>
+        <v>5940</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4050</v>
+        <v>3210</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="8" t="n">
-        <v>55.7</v>
-      </c>
+      <c r="J21" s="8" t="n"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>aniway</t>
+          <t>奥维地图</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1535,39 +1514,37 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>vega app</t>
+          <t>spam challenge list</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://vegaapp.vercel.app/</t>
+          <t>https://scl.vercel.app/</t>
         </is>
       </c>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="4" t="n">
-        <v>10950</v>
+        <v>6880</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>3370</v>
+        <v>1850</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="8" t="n">
-        <v>59.7</v>
-      </c>
+      <c r="J22" s="8" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>vega app</t>
+          <t>spam challenge list</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1579,39 +1556,37 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>奥维地图</t>
+          <t>country draw</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://ov-map.vercel.app/</t>
+          <t>https://country-draw.vercel.app/</t>
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="4" t="n">
-        <v>6210</v>
+        <v>44670</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>3210</v>
+        <v>1820</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="8" t="n">
-        <v>38.5</v>
-      </c>
+      <c r="J23" s="8" t="n"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>奥维地图</t>
+          <t>country draw</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1623,39 +1598,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>lunaranime</t>
+          <t>роблокс войти</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://lunar-zeta.vercel.app/</t>
+          <t>https://roblox-login-orpin.vercel.app/</t>
         </is>
       </c>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="4" t="n">
-        <v>35220</v>
+        <v>660</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2020</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>20</v>
-      </c>
+        <v>1710</v>
+      </c>
+      <c r="H24" s="7" t="n"/>
       <c r="I24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>8</v>
+        <v>81.2</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>lunaranime</t>
+          <t>роблокс войти</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -1667,17 +1640,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>country draw</t>
+          <t>twitter aura</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://country-draw.vercel.app/</t>
+          <t>https://twitter-aura-main.vercel.app/</t>
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="4" t="n">
-        <v>41240</v>
+        <v>1750</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0</v>
@@ -1686,20 +1659,20 @@
         <v>0</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1820</v>
+        <v>1450</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>7.8</v>
+        <v>57.7</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>country draw</t>
+          <t>twitter aura</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -1711,39 +1684,39 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ffxiv weather</t>
+          <t>snail ide</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://eorzea-weather.vercel.app/</t>
+          <t>https://snailshare.vercel.app/</t>
         </is>
       </c>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="4" t="n">
-        <v>830</v>
+        <v>1170</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>1790</v>
+        <v>1430</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>32.9</v>
+        <v>93.7</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>ffxiv weather</t>
+          <t>snail ide</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -1755,37 +1728,39 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>роблокс войти</t>
+          <t>watchwave</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://roblox-login-orpin.vercel.app/</t>
+          <t>https://watch-wave-beta.vercel.app/</t>
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="4" t="n">
-        <v>800</v>
+        <v>6140</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>1710</v>
-      </c>
-      <c r="H27" s="7" t="n"/>
+        <v>1420</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>21</v>
+      </c>
       <c r="I27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>81.2</v>
+        <v>45.8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>роблокс войти</t>
+          <t>watchwave</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -1797,39 +1772,37 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>satisfactory layout planner</t>
+          <t>电影猎手</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://satisfactory-layout-planner.vercel.app/</t>
+          <t>https://h5-beta.vercel.app/</t>
         </is>
       </c>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="4" t="n">
-        <v>1420</v>
+        <v>1780</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>1280</v>
+        <v>1030</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="8" t="n">
-        <v>42</v>
-      </c>
+      <c r="J28" s="8" t="n"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>satisfactory layout planner</t>
+          <t>电影猎手</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -1841,35 +1814,37 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>作戦室</t>
+          <t>filmhaven</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://jervis.vercel.app/</t>
+          <t>https://film-haven.vercel.app/</t>
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="4" t="n">
-        <v>1130</v>
+        <v>3170</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>880</v>
-      </c>
-      <c r="H29" s="7" t="n"/>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="8" t="n">
-        <v>43.7</v>
-      </c>
+        <v>950</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="n"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>作戦室</t>
+          <t>filmhaven</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -1881,39 +1856,37 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>homer's web page</t>
+          <t>the rhyme game</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://homers-webpage.vercel.app/</t>
+          <t>https://rhyme-game2026.vercel.app/</t>
         </is>
       </c>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="4" t="n">
-        <v>1300</v>
+        <v>36270</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="8" t="n">
-        <v>53.4</v>
-      </c>
+      <c r="J30" s="8" t="n"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>homer's web page</t>
+          <t>the rhyme game</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -1925,39 +1898,33 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12axes</t>
+          <t>作戦室</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://12axes.vercel.app/en</t>
+          <t>https://jervis.vercel.app/</t>
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="4" t="n">
-        <v>8370</v>
+        <v>1470</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>560</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="8" t="n">
-        <v>44.1</v>
-      </c>
+        <v>880</v>
+      </c>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="7" t="n"/>
+      <c r="J31" s="8" t="n"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12axes</t>
+          <t>作戦室</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -1969,17 +1936,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>生フェス</t>
+          <t>amicro</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://namafes2026.vercel.app/</t>
+          <t>https://amicro.vercel.app/</t>
         </is>
       </c>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="4" t="n">
-        <v>5550</v>
+        <v>3380</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>0</v>
@@ -1988,16 +1955,18 @@
         <v>0</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>480</v>
-      </c>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="8" t="n">
-        <v>45</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>生フェス</t>
+          <t>amicro</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2009,17 +1978,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>oaken tower builds</t>
+          <t>сравнение мышек</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://oaken-tower-builders-hub.vercel.app/</t>
+          <t>https://eloshapes.vercel.app/mouse/compare</t>
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="4" t="n">
-        <v>3470</v>
+        <v>2760</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>0</v>
@@ -2028,16 +1997,16 @@
         <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>390</v>
+        <v>750</v>
       </c>
       <c r="H33" s="7" t="n"/>
-      <c r="I33" s="7" t="n"/>
-      <c r="J33" s="8" t="n">
-        <v>43.3</v>
-      </c>
+      <c r="I33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>oaken tower builds</t>
+          <t>сравнение мышек</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2049,17 +2018,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>弥生給与 ダウンロード</t>
+          <t>12axes</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://yayoi-migration-checker.vercel.app/guide</t>
+          <t>https://12axes.vercel.app/en</t>
         </is>
       </c>
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="4" t="n">
-        <v>0</v>
+        <v>9460</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>0</v>
@@ -2068,16 +2037,20 @@
         <v>0</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>390</v>
-      </c>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
+        <v>560</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J34" s="8" t="n">
-        <v>27.2</v>
+        <v>44.1</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>弥生給与 ダウンロード</t>
+          <t>12axes</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2089,39 +2062,39 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>denouement demon list</t>
+          <t>prompt splitter</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://denouementdl.vercel.app/</t>
+          <t>https://chatgpt-prompt-splitter.vercel.app/</t>
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="4" t="n">
-        <v>780</v>
+        <v>1310</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>380</v>
+        <v>450</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>47.8</v>
+        <v>46.4</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>denouement demon list</t>
+          <t>prompt splitter</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2133,39 +2106,35 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>avatar guesser</t>
+          <t>oaken tower builds</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://avatarguesser.vercel.app/avatar</t>
+          <t>https://oaken-tower-builders-hub.vercel.app/</t>
         </is>
       </c>
       <c r="C36" s="3" t="n"/>
       <c r="D36" s="4" t="n">
-        <v>2330</v>
+        <v>3930</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>280</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>0</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
       <c r="J36" s="8" t="n">
-        <v>38.4</v>
+        <v>43.3</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>avatar guesser</t>
+          <t>oaken tower builds</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2177,39 +2146,33 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>the floor online game</t>
+          <t>弥生給与 ダウンロード</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://the-floor-game.vercel.app/</t>
+          <t>https://yayoi-migration-checker.vercel.app/guide</t>
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="4" t="n">
-        <v>2560</v>
+        <v>0</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>240</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <v>50.4</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="8" t="n"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>the floor online game</t>
+          <t>弥生給与 ダウンロード</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2221,17 +2184,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>fire emblem wordle</t>
+          <t>denouement demon list</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://fire-guesser.vercel.app/</t>
+          <t>https://denouementdl.vercel.app/</t>
         </is>
       </c>
       <c r="C38" s="3" t="n"/>
       <c r="D38" s="4" t="n">
-        <v>3650</v>
+        <v>810</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>0</v>
@@ -2240,20 +2203,18 @@
         <v>0</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>210</v>
+        <v>380</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>53.5</v>
-      </c>
+      <c r="J38" s="8" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>fire emblem wordle</t>
+          <t>denouement demon list</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -2265,59 +2226,51 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>enshrouded all blocks</t>
+          <t>simulador del mundial 2022</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://enshrouded-blocks.vercel.app/</t>
+          <t>https://qatar-worldcup-simulator.vercel.app/</t>
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
-      <c r="D39" s="4" t="n">
-        <v>1060</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
       <c r="G39" s="6" t="n">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="H39" s="7" t="n"/>
       <c r="I39" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="8" t="n">
-        <v>52.3</v>
-      </c>
+      <c r="J39" s="8" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>enshrouded all blocks</t>
+          <t>simulador del mundial 2022</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>dynamic island for windows</t>
+          <t>clipforge</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://apple-notch.vercel.app/</t>
+          <t>https://clipforge.vercel.app/</t>
         </is>
       </c>
       <c r="C40" s="3" t="n"/>
       <c r="D40" s="4" t="n">
-        <v>3620</v>
+        <v>16660</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>0</v>
@@ -2326,18 +2279,16 @@
         <v>0</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="H40" s="7" t="n"/>
       <c r="I40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="8" t="n">
-        <v>45.6</v>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="J40" s="8" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>dynamic island for windows</t>
+          <t>clipforge</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -2349,37 +2300,37 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>competence lab</t>
+          <t>avatar guesser</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://eva-rouge-zeta.vercel.app/login</t>
+          <t>https://avatarguesser.vercel.app/avatar</t>
         </is>
       </c>
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="4" t="n">
-        <v>2410</v>
+        <v>2700</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>110</v>
-      </c>
-      <c r="H41" s="7" t="n"/>
+        <v>280</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>15</v>
+      </c>
       <c r="I41" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="8" t="n">
-        <v>26.3</v>
-      </c>
+      <c r="J41" s="8" t="n"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>competence lab</t>
+          <t>avatar guesser</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -2391,17 +2342,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>maganghub tracker</t>
+          <t>hoopheads</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://maganghub-tracker-tau.vercel.app/</t>
+          <t>https://hoopheads.vercel.app/</t>
         </is>
       </c>
       <c r="C42" s="3" t="n"/>
       <c r="D42" s="4" t="n">
-        <v>13530</v>
+        <v>1490</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
@@ -2410,20 +2361,18 @@
         <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="8" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="J42" s="8" t="n"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>maganghub tracker</t>
+          <t>hoopheads</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -2435,37 +2384,35 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>urv ai</t>
+          <t>классификатор банков 1с скачать</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://urv-ai.vercel.app/</t>
+          <t>https://1c-expert.vercel.app/articles/k/kl/klassifikator-bankov-gde-vzyat-fajl-dlya-1s.html</t>
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="4" t="n">
-        <v>2670</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="H43" s="7" t="n"/>
-      <c r="I43" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I43" s="7" t="n"/>
       <c r="J43" s="8" t="n">
-        <v>61.3</v>
+        <v>14.1</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>urv ai</t>
+          <t>классификатор банков 1с скачать</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -2477,17 +2424,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>blackhawk rescue mission 5 zombie map</t>
+          <t>cobe npm</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://brm5-map.vercel.app/</t>
+          <t>https://cobe.vercel.app/</t>
         </is>
       </c>
       <c r="C44" s="3" t="n"/>
       <c r="D44" s="4" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>0</v>
@@ -2496,20 +2443,18 @@
         <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>19</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H44" s="7" t="n"/>
       <c r="I44" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>52.1</v>
+        <v>54.7</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>blackhawk rescue mission 5 zombie map</t>
+          <t>cobe npm</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -2521,17 +2466,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>學測倒數</t>
+          <t>maganghub tracker</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://ceecc.vercel.app/</t>
+          <t>https://maganghub-tracker-tau.vercel.app/</t>
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="4" t="n">
-        <v>1470</v>
+        <v>16340</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0</v>
@@ -2540,18 +2485,20 @@
         <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="H45" s="7" t="n"/>
+        <v>90</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>18</v>
+      </c>
       <c r="I45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="8" t="n">
-        <v>35.5</v>
+        <v>29.8</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>學測倒數</t>
+          <t>maganghub tracker</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -2563,17 +2510,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>курсоры для роблокс</t>
+          <t>stremio profile addon</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://cursor-x.vercel.app/</t>
+          <t>https://stremio-account-addon-cloner.vercel.app/</t>
         </is>
       </c>
       <c r="C46" s="3" t="n"/>
       <c r="D46" s="4" t="n">
-        <v>1020</v>
+        <v>760</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>0</v>
@@ -2582,18 +2529,16 @@
         <v>0</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H46" s="7" t="n"/>
-      <c r="I46" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I46" s="7" t="n"/>
       <c r="J46" s="8" t="n">
-        <v>14.3</v>
+        <v>50.6</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>курсоры для роблокс</t>
+          <t>stremio profile addon</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -2605,39 +2550,35 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>pantauloker</t>
+          <t>курсоры для роблокс</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://pantauloker.vercel.app/</t>
+          <t>https://cursor-x.vercel.app/</t>
         </is>
       </c>
       <c r="C47" s="3" t="n"/>
       <c r="D47" s="4" t="n">
-        <v>13170</v>
+        <v>1260</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>19</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="H47" s="7" t="n"/>
       <c r="I47" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="8" t="n">
-        <v>26.5</v>
-      </c>
+      <c r="J47" s="8" t="n"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>pantauloker</t>
+          <t>курсоры для роблокс</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -2649,37 +2590,44 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>포도알</t>
+          <t>bac story</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://grape-simulation.vercel.app/</t>
+          <t>https://bacstory.vercel.app/
+https://bacstory.vercel.app/oqba
+https://bacstory.vercel.app/simulation
+https://bacstory.vercel.app/orientation
+https://bacstory.vercel.app/university/speciality/ensc
+https://bacstory.vercel.app/resources
+https://bacstory.vercel.app/tools
+https://bacstory.vercel.app/advertise
+https://bacstory.vercel.app/bac-topics
+https://bacstory.vercel.app/bac-2026-lp-topics</t>
         </is>
       </c>
       <c r="C48" s="3" t="n"/>
       <c r="D48" s="4" t="n">
-        <v>1740</v>
+        <v>83970</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H48" s="7" t="n"/>
       <c r="I48" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="8" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="J48" s="8" t="n"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>포도알</t>
+          <t>bac story</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -2691,37 +2639,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>lums pro planner</t>
+          <t>pantauloker</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://lums-course-scheduler.vercel.app/</t>
+          <t>https://pantauloker.vercel.app/</t>
         </is>
       </c>
       <c r="C49" s="3" t="n"/>
       <c r="D49" s="4" t="n">
-        <v>20730</v>
+        <v>15650</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="H49" s="7" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>19</v>
+      </c>
       <c r="I49" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="8" t="n">
-        <v>47</v>
-      </c>
+      <c r="J49" s="8" t="n"/>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>lums pro planner</t>
+          <t>pantauloker</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -2733,37 +2681,35 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>tailwind css to css converter</t>
+          <t>포도알</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://tailwind-to-css.vercel.app/</t>
+          <t>https://grape-simulation.vercel.app/</t>
         </is>
       </c>
       <c r="C50" s="3" t="n"/>
       <c r="D50" s="4" t="n">
-        <v>760</v>
+        <v>1640</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H50" s="7" t="n"/>
       <c r="I50" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="8" t="n">
-        <v>46.2</v>
-      </c>
+      <c r="J50" s="8" t="n"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>tailwind css to css converter</t>
+          <t>포도알</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -2775,17 +2721,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>こえはかる</t>
+          <t>hanan irfan</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://voice-impression-checker.vercel.app/</t>
+          <t>https://hananirfanportfolio.vercel.app/</t>
         </is>
       </c>
       <c r="C51" s="3" t="n"/>
       <c r="D51" s="4" t="n">
-        <v>9330</v>
+        <v>820</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
@@ -2794,16 +2740,16 @@
         <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H51" s="7" t="n"/>
-      <c r="I51" s="7" t="n"/>
-      <c r="J51" s="8" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="I51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="8" t="n"/>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>こえはかる</t>
+          <t>hanan irfan</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -2815,35 +2761,35 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>夢女子すごろく</t>
+          <t>lums pro planner</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://yumejoshi-sugoroku.vercel.app/?share=card</t>
+          <t>https://lums-course-scheduler.vercel.app/</t>
         </is>
       </c>
       <c r="C52" s="3" t="n"/>
       <c r="D52" s="4" t="n">
-        <v>5320</v>
+        <v>24200</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n"/>
-      <c r="J52" s="8" t="n">
-        <v>70.40000000000001</v>
-      </c>
+      <c r="I52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="8" t="n"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>夢女子すごろく</t>
+          <t>lums pro planner</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -2855,77 +2801,73 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>나무위키 스피드런</t>
+          <t>enshrouded wall blocks</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://tree-speed.vercel.app/</t>
+          <t>https://enshrouded-blocks.vercel.app/</t>
         </is>
       </c>
       <c r="C53" s="3" t="n"/>
-      <c r="D53" s="4" t="n">
-        <v>4080</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0</v>
-      </c>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
       <c r="G53" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H53" s="7" t="n"/>
       <c r="I53" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J53" s="8" t="n">
-        <v>62.5</v>
+        <v>42.7</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>나무위키 스피드런</t>
+          <t>enshrouded wall blocks</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>both（SIM+SEM）</t>
+          <t>sem_only（仅 SEM）</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12axes vercel app</t>
+          <t>jiit shelf</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://12axes.vercel.app/</t>
+          <t>https://jiitshelf.vercel.app/</t>
         </is>
       </c>
       <c r="C54" s="3" t="n"/>
       <c r="D54" s="4" t="n">
-        <v>3370</v>
+        <v>3110</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H54" s="7" t="n"/>
-      <c r="I54" s="7" t="n"/>
+      <c r="I54" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J54" s="8" t="n">
-        <v>48.4</v>
+        <v>18.3</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>12axes vercel app</t>
+          <t>jiit shelf</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -2937,35 +2879,37 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>yg ran online</t>
+          <t>pcie simulator</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://ygmobile.vercel.app/</t>
+          <t>https://pcie-simulator.vercel.app/</t>
         </is>
       </c>
       <c r="C55" s="3" t="n"/>
       <c r="D55" s="4" t="n">
-        <v>3320</v>
+        <v>500</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
+      <c r="I55" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="J55" s="8" t="n">
-        <v>55.3</v>
+        <v>36.9</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>yg ran online</t>
+          <t>pcie simulator</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -2977,17 +2921,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>supercode cli</t>
+          <t>gesture synth weld vercel</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://supercodeai.vercel.app/</t>
+          <t>https://gesture-synth-weld.vercel.app/</t>
         </is>
       </c>
       <c r="C56" s="3" t="n"/>
       <c r="D56" s="4" t="n">
-        <v>2620</v>
+        <v>44680</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0</v>
@@ -3001,11 +2945,11 @@
       <c r="H56" s="7" t="n"/>
       <c r="I56" s="7" t="n"/>
       <c r="J56" s="8" t="n">
-        <v>38.9</v>
+        <v>29.8</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>supercode cli</t>
+          <t>gesture synth weld vercel</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -3017,17 +2961,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>gifsync vercel</t>
+          <t>zeroscript</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://gifsync.vercel.app/</t>
+          <t>https://zeroscript-five.vercel.app/</t>
         </is>
       </c>
       <c r="C57" s="3" t="n"/>
       <c r="D57" s="4" t="n">
-        <v>1710</v>
+        <v>12710</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0</v>
@@ -3039,13 +2983,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="7" t="n"/>
-      <c r="I57" s="7" t="n"/>
-      <c r="J57" s="8" t="n">
-        <v>59</v>
-      </c>
+      <c r="I57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="8" t="n"/>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>gifsync vercel</t>
+          <t>zeroscript</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -3057,20 +3001,20 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>jiit pulse</t>
+          <t>こえはかる</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://jiit-pulse.vercel.app/</t>
+          <t>https://voice-impression-checker.vercel.app/</t>
         </is>
       </c>
       <c r="C58" s="3" t="n"/>
       <c r="D58" s="4" t="n">
-        <v>1570</v>
+        <v>12460</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0</v>
@@ -3080,12 +3024,10 @@
       </c>
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="7" t="n"/>
-      <c r="J58" s="8" t="n">
-        <v>51.7</v>
-      </c>
+      <c r="J58" s="8" t="n"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>jiit pulse</t>
+          <t>こえはかる</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -3097,20 +3039,20 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>think of you vercel app</t>
+          <t>zestflix</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://think-of-you.vercel.app/</t>
+          <t>https://zetflix-tv.vercel.app/search</t>
         </is>
       </c>
       <c r="C59" s="3" t="n"/>
       <c r="D59" s="4" t="n">
-        <v>1530</v>
+        <v>11350</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>0</v>
@@ -3120,12 +3062,10 @@
       </c>
       <c r="H59" s="7" t="n"/>
       <c r="I59" s="7" t="n"/>
-      <c r="J59" s="8" t="n">
-        <v>54.9</v>
-      </c>
+      <c r="J59" s="8" t="n"/>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>think of you vercel app</t>
+          <t>zestflix</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -3137,17 +3077,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>fe guess</t>
+          <t>learn jh</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://fe-guess.vercel.app/</t>
+          <t>https://learnjh.vercel.app/</t>
         </is>
       </c>
       <c r="C60" s="3" t="n"/>
       <c r="D60" s="4" t="n">
-        <v>1360</v>
+        <v>6530</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>0</v>
@@ -3160,12 +3100,10 @@
       </c>
       <c r="H60" s="7" t="n"/>
       <c r="I60" s="7" t="n"/>
-      <c r="J60" s="8" t="n">
-        <v>37</v>
-      </c>
+      <c r="J60" s="8" t="n"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>fe guess</t>
+          <t>learn jh</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -3177,17 +3115,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>herramientas pokemon idle world</t>
+          <t>나무위키 스피드런</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://piwtools.vercel.app/hunt</t>
+          <t>https://tree-speed.vercel.app/</t>
         </is>
       </c>
       <c r="C61" s="3" t="n"/>
       <c r="D61" s="4" t="n">
-        <v>1240</v>
+        <v>4820</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0</v>
@@ -3199,13 +3137,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="7" t="n"/>
-      <c r="I61" s="7" t="n"/>
-      <c r="J61" s="8" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="I61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="8" t="n"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>herramientas pokemon idle world</t>
+          <t>나무위키 스피드런</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -3217,17 +3155,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>simulator pcie lanea</t>
+          <t>12axes vercel app</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://pcie-simulator.vercel.app/</t>
+          <t>https://12axes.vercel.app/</t>
         </is>
       </c>
       <c r="C62" s="3" t="n"/>
       <c r="D62" s="4" t="n">
-        <v>920</v>
+        <v>4740</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>0</v>
@@ -3240,12 +3178,10 @@
       </c>
       <c r="H62" s="7" t="n"/>
       <c r="I62" s="7" t="n"/>
-      <c r="J62" s="8" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="J62" s="8" t="n"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>simulator pcie lanea</t>
+          <t>12axes vercel app</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -3257,17 +3193,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>컴프야 스쿼드메이커</t>
+          <t>supercode cli</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://kbo-squadmaker.vercel.app/</t>
+          <t>https://supercodeai.vercel.app/</t>
         </is>
       </c>
       <c r="C63" s="3" t="n"/>
       <c r="D63" s="4" t="n">
-        <v>270</v>
+        <v>4060</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
@@ -3281,11 +3217,11 @@
       <c r="H63" s="7" t="n"/>
       <c r="I63" s="7" t="n"/>
       <c r="J63" s="8" t="n">
-        <v>41.4</v>
+        <v>38.9</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>컴프야 스쿼드메이커</t>
+          <t>supercode cli</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -3297,54 +3233,60 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>auto sbc complete multiple sbc's at one time</t>
+          <t>awsome arcade</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://autopilotsbc.vercel.app/</t>
+          <t>https://awesome-arcade.vercel.app/</t>
         </is>
       </c>
       <c r="C64" s="3" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
+      <c r="D64" s="4" t="n">
+        <v>3760</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G64" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="7" t="n"/>
       <c r="I64" s="7" t="n"/>
       <c r="J64" s="8" t="n">
-        <v>30.7</v>
+        <v>14.3</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>auto sbc complete multiple sbc's at one time</t>
+          <t>awsome arcade</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>back to the dawn jailbreak quests</t>
+          <t>jiit pulse</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>https://back-to-the-dawn-data.vercel.app/en/walkthrough</t>
+          <t>https://jiit-pulse.vercel.app/</t>
         </is>
       </c>
       <c r="C65" s="3" t="n"/>
       <c r="D65" s="4" t="n">
-        <v>0</v>
+        <v>2860</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>0</v>
@@ -3355,11 +3297,11 @@
       <c r="H65" s="7" t="n"/>
       <c r="I65" s="7" t="n"/>
       <c r="J65" s="8" t="n">
-        <v>33.5</v>
+        <v>51.7</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>back to the dawn jailbreak quests</t>
+          <t>jiit pulse</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -3371,18 +3313,24 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>courserekt</t>
+          <t>弗一把</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>https://courserekt.vercel.app/</t>
+          <t>https://guess-cspro.vercel.app/</t>
         </is>
       </c>
       <c r="C66" s="3" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
+      <c r="D66" s="4" t="n">
+        <v>2220</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G66" s="6" t="n">
         <v>0</v>
       </c>
@@ -3391,33 +3339,33 @@
         <v>0</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>37.6</v>
+        <v>51.3</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>courserekt</t>
+          <t>弗一把</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>d-link dir-825 как репитер: настройка в режиме повторителя wi-fi</t>
+          <t>ponnie review</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>https://wi-fi-gid.vercel.app/articles/d/di/dir-825-nastroit-kak-repiter-wifi.html</t>
+          <t>https://ponniereview.vercel.app/</t>
         </is>
       </c>
       <c r="C67" s="3" t="n"/>
       <c r="D67" s="4" t="n">
-        <v>0</v>
+        <v>2160</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>0</v>
@@ -3431,11 +3379,11 @@
       <c r="H67" s="7" t="n"/>
       <c r="I67" s="7" t="n"/>
       <c r="J67" s="8" t="n">
-        <v>25.6</v>
+        <v>67</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>d-link dir-825 как репитер: настройка в режиме повторителя wi-fi</t>
+          <t>ponnie review</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -3447,20 +3395,20 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>huawei echolife hg8245h5 скорость интернета</t>
+          <t>think of you vercel app</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>https://wi-fi-gid.vercel.app/articles/h/hg/hg8245h-kak-uvelichit-skorost-wifi-na-routere.html</t>
+          <t>https://think-of-you.vercel.app/</t>
         </is>
       </c>
       <c r="C68" s="3" t="n"/>
       <c r="D68" s="4" t="n">
-        <v>0</v>
+        <v>1760</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>0</v>
@@ -3470,12 +3418,10 @@
       </c>
       <c r="H68" s="7" t="n"/>
       <c r="I68" s="7" t="n"/>
-      <c r="J68" s="8" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="J68" s="8" t="n"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>huawei echolife hg8245h5 скорость интернета</t>
+          <t>think of you vercel app</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -3487,17 +3433,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>kak izmenit mac adress</t>
+          <t>fe guess</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>https://wi-fi-gid.vercel.app/articles/k/ka/kak-izmenit-mac-wifi.html</t>
+          <t>https://fe-guess.vercel.app/</t>
         </is>
       </c>
       <c r="C69" s="3" t="n"/>
       <c r="D69" s="4" t="n">
-        <v>0</v>
+        <v>1610</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>0</v>
@@ -3510,12 +3456,10 @@
       </c>
       <c r="H69" s="7" t="n"/>
       <c r="I69" s="7" t="n"/>
-      <c r="J69" s="8" t="n">
-        <v>32.1</v>
-      </c>
+      <c r="J69" s="8" t="n"/>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>kak izmenit mac adress</t>
+          <t>fe guess</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -3527,17 +3471,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>mtproto.ru прокси для телеграм список</t>
+          <t>캄몬 카드</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>https://mtproto-ru.vercel.app/example-other.php</t>
+          <t>https://cardgacha.vercel.app/</t>
         </is>
       </c>
       <c r="C70" s="3" t="n"/>
       <c r="D70" s="4" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>0</v>
@@ -3550,12 +3494,10 @@
       </c>
       <c r="H70" s="7" t="n"/>
       <c r="I70" s="7" t="n"/>
-      <c r="J70" s="8" t="n">
-        <v>31.2</v>
-      </c>
+      <c r="J70" s="8" t="n"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>mtproto.ru прокси для телеграм список</t>
+          <t>캄몬 카드</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -3567,87 +3509,95 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>pokeidle ferramentas</t>
+          <t>herramientas pokemon idle world</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://piwtools.vercel.app/</t>
+          <t>https://piwtools.vercel.app/hunt</t>
         </is>
       </c>
       <c r="C71" s="3" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
+      <c r="D71" s="4" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G71" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="7" t="n"/>
-      <c r="J71" s="8" t="n">
-        <v>32.3</v>
-      </c>
+      <c r="J71" s="8" t="n"/>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>pokeidle ferramentas</t>
+          <t>herramientas pokemon idle world</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>wow m  title</t>
+          <t>power grid jump space</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://mplus-title.vercel.app/mn-season-1</t>
+          <t>https://jump-space-grid-optimizer.vercel.app/</t>
         </is>
       </c>
       <c r="C72" s="3" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
+      <c r="D72" s="4" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G72" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="7" t="n"/>
-      <c r="I72" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="I72" s="7" t="n"/>
       <c r="J72" s="8" t="n">
-        <v>50.3</v>
+        <v>42.4</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>wow m  title</t>
+          <t>power grid jump space</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>вгыеук слив антифриза</t>
+          <t>gifting back to the dawn</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://renault-guide.vercel.app/articles/z/za/zamena-antifriza-daster.html</t>
+          <t>https://back-to-the-dawn-data.vercel.app/en/gift</t>
         </is>
       </c>
       <c r="C73" s="3" t="n"/>
       <c r="D73" s="4" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>0</v>
@@ -3661,11 +3611,11 @@
       <c r="H73" s="7" t="n"/>
       <c r="I73" s="7" t="n"/>
       <c r="J73" s="8" t="n">
-        <v>18.9</v>
+        <v>33.7</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>вгыеук слив антифриза</t>
+          <t>gifting back to the dawn</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -3677,17 +3627,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>изменение размера изображения онлайн без потери качества</t>
+          <t>twitter aura2 vercel</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://fastfileconvert.vercel.app/ru/tools/image-resizer</t>
+          <t>https://twitter-aura2.vercel.app/</t>
         </is>
       </c>
       <c r="C74" s="3" t="n"/>
       <c r="D74" s="4" t="n">
-        <v>0</v>
+        <v>440</v>
       </c>
       <c r="E74" s="5" t="n">
         <v>0</v>
@@ -3701,11 +3651,11 @@
       <c r="H74" s="7" t="n"/>
       <c r="I74" s="7" t="n"/>
       <c r="J74" s="8" t="n">
-        <v>22.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>изменение размера изображения онлайн без потери качества</t>
+          <t>twitter aura2 vercel</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -3717,46 +3667,52 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>как открыть лайтматик файлы</t>
+          <t>1с ут печатная форма м15</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://litematic-viewer-x1oa.vercel.app/</t>
+          <t>https://1c-expert.vercel.app/articles/f/fo/forma-m15-gde-v-1s.html</t>
         </is>
       </c>
       <c r="C75" s="3" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
+      <c r="D75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G75" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="7" t="n"/>
       <c r="J75" s="8" t="n">
-        <v>13.3</v>
+        <v>4.7</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>как открыть лайтматик файлы</t>
+          <t>1с ут печатная форма м15</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>sem_only（仅 SEM）</t>
+          <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>熱中症 連絡 体制 表 エクセル</t>
+          <t>back to the dawn jailbreak quests</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://heatstroke-navi.vercel.app/articles/heatstroke-reporting-system-template</t>
+          <t>https://back-to-the-dawn-data.vercel.app/en/walkthrough</t>
         </is>
       </c>
       <c r="C76" s="3" t="n"/>
@@ -3775,21 +3731,509 @@
       <c r="H76" s="7" t="n"/>
       <c r="I76" s="7" t="n"/>
       <c r="J76" s="8" t="n">
-        <v>2.6</v>
+        <v>33.5</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
+          <t>back to the dawn jailbreak quests</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>krypton addon sus</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>https://krypton-mc.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n"/>
+      <c r="D77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>krypton addon sus</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>mtproto.ru прокси для телеграм список</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>https://mtproto-ru.vercel.app/example-other.php</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n"/>
+      <c r="D78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="7" t="n"/>
+      <c r="I78" s="7" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>mtproto.ru прокси для телеграм список</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>pokeidle ferramentas</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>https://piwtools.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="5" t="n"/>
+      <c r="F79" s="5" t="n"/>
+      <c r="G79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="8" t="n"/>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>pokeidle ferramentas</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>wow m  title</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>https://mplus-title.vercel.app/mn-season-1</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="7" t="n"/>
+      <c r="I80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="8" t="n"/>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>wow m  title</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>изменение размера изображения онлайн без потери качества</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>https://fastfileconvert.vercel.app/ru/tools/image-resizer</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n"/>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
+      <c r="J81" s="8" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>изменение размера изображения онлайн без потери качества</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>как в зуп убрать задолженность по зарплате прошлых периодов</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>https://1c-expert.vercel.app/articles/k/ka/kak-spisat-zadolzhennost-po-zarplate-proshlykh-let-v-1s-83-zup.html</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n"/>
+      <c r="D82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="7" t="n"/>
+      <c r="J82" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>как в зуп убрать задолженность по зарплате прошлых периодов</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>как заменить уплотнитель на холодильнике бош</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>https://master-shin.vercel.app/articles/k/ka/kak-pomenyat-rezinku-na-kholodilnike-bosh.html</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n"/>
+      <c r="D83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="7" t="n"/>
+      <c r="I83" s="7" t="n"/>
+      <c r="J83" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>как заменить уплотнитель на холодильнике бош</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>какие виды расчета являются базовыми в 1с</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>https://1c-expert.vercel.app/articles/1/1s/1s-chto-takoe-bazovye-vidy-rascheta-vytesnyayushchie-vidy-rascheta-vedushchie-vidy-rascheta.html</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n"/>
+      <c r="D84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="7" t="n"/>
+      <c r="I84" s="7" t="n"/>
+      <c r="J84" s="8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>какие виды расчета являются базовыми в 1с</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>печать фото в эпсон 132</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>https://printer-e.vercel.app/articles/k/ka/kak-napechatat-foto-10kh15-na-printere-epson-l132.html</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n"/>
+      <c r="D85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
+      <c r="J85" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>печать фото в эпсон 132</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>рассчитать энд портал</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>https://find-ender.vercel.app/</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+      <c r="J86" s="8" t="n"/>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>рассчитать энд портал</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>sem_only（仅 SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>ремонт салонного вентилятора лада икс рей</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>https://lada-spravka.vercel.app/articles/v/ve/ventilyator-pechki-lada-kh-rej.html</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n"/>
+      <c r="D87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>ремонт салонного вентилятора лада икс рей</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>снимаем главный цилиндр сцепления на буханке</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>https://uaz-portal.vercel.app/articles/k/ka/kak-snyat-glavnyj-tsilindr-stsepleniya-uaz-bukhanka.html?ysclid=mrpyrpcns9769636925</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n"/>
+      <c r="D88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>снимаем главный цилиндр сцепления на буханке</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
           <t>熱中症 連絡 体制 表 エクセル</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>https://heatstroke-navi.vercel.app/articles/heatstroke-reporting-system-template</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n"/>
+      <c r="D89" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>熱中症 連絡 体制 表 エクセル</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>both（SIM+SEM）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L76"/>
+  <autoFilter ref="A1:L89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>